--- a/extenbooks/ES1301.xlsx
+++ b/extenbooks/ES1301.xlsx
@@ -921,11 +921,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_assembly</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1301 — NSW/GDP Extended (Moos 2017) — PENDING</t>
+          <t># ES1301 — Moos 2017 NSW/GDP Extended</t>
         </is>
       </c>
     </row>
@@ -1097,87 +1097,67 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: validated_book_and_extension.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Moos's NSW1 / GDP. 54 rows 1959-2012. First=-1.46%, last=+6.73%. NSW positive post-2000 in Moos's reconciliation.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>needs GDP + Moos NSW</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Moos's reconciled NSW dataset (cached at `Moos_nsw_reconciled.csv`, column `nsw1`) / BEA NIPA 1.7.5 GDP.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Moos nsw_reconciled column nsw1/2 / BEA GDP</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1301.xlsx
+++ b/extenbooks/ES1301.xlsx
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 4</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1959–2024</t>
+          <t>1959-2012</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1074,54 +1074,63 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1301-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Moos 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1301 — Moos 2017 NSW/GDP Extended</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1301 — Moos 2017 NSW/GDP Extended</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Moos's NSW1 / GDP. 54 rows 1959-2012. First=-1.46%, last=+6.73%. NSW positive post-2000 in Moos's reconciliation.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Moos's NSW1 / GDP. 54 rows 1959-2012. First=-1.46%, last=+6.73%. NSW positive post-2000 in Moos's reconciliation.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1142,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Moos's reconciled NSW dataset (cached at `Moos_nsw_reconciled.csv`, column `nsw1`) / BEA NIPA 1.7.5 GDP.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1154,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Moos's reconciled NSW dataset (cached at `Moos_nsw_reconciled.csv`, column `nsw1`) / BEA NIPA 1.7.5 GDP.</t>
         </is>
       </c>
     </row>
@@ -1156,6 +1165,18 @@
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1172,10 +1193,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1200,196 +1221,228 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Moos (2017) replicates and extends Shaikh &amp; Tonak (2002), computing NSW/GDP for 1959-2012. The methodology follows Shaikh &amp; Tonak: NSW = E1 + E2*LS - T1 - T2*LS, where E1 = direct labor benefits entirely allocated to labor (income support, Social Security, public assistance, housing); E2 = social consumption expenditures partially allocated by labor share LS; T1 = employee + employer Social Security contributions; T2 = personal income and property taxes allocated by LS. Moos primarily uses NSW/GDP as the denominator (citing Shaikh 2003), whereas Shaikh &amp; Tonak (2002) primarily used NSW/EC.</t>
+          <t>This paper replicates the methodology and extends the data series in Shaikh and Tonak (2000) in order to examine fiscal transfers between the state and workers in the United States in the 21st century. Strikingly, the updated net social wage data reveals a sizable deviation starting in 2002, with much higher positive net social wages for a decade. In fact, the net social wage rises to a historic high of positive 8.6 percent of GDP in 2010.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 2 pp.3-4; full_transcription.md Section 2 Net Social Wage Methodology; DECISION_LOG.md DEC-013</t>
+          <t>Moos 2017, Introduction, p.2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEC-013 (2026-05-06): The ST2 implementation (P21) uses NSW = E1 - (T1 + T2*LS) — direct social benefits minus taxes. Government consumption expenditure E2 (education, health, transportation from NIPA T3.16) is loaded by L17 but NOT included in the NSW computation. With E2 excluded, P21 produces a 1959-1997 overlap mean of 0.013, within 0.002 of Moos's published mean of 0.011. Including E2 at any positive alpha overshoots the 0.011 target substantially (at alpha=1.0 mean=0.071). The standard Shaikh-Tonak/Moos formula measures net fiscal transfer to workers: direct benefits minus taxes only.</t>
+          <t>NetSocialWage = TotalLaborBenefits − TotalLaborTaxes    (1) ... TotalLaborBenefits = E1 + E2 ∗ LS    (2) ... TotalLaborTaxes = T1 + T2 ∗ LS    (3)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-013</t>
+          <t>Moos 2017, Net Social Wage Methodology, p.3-4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Moos (2017) finds a major post-2001 structural break. Period 1959-2000: NSW/GDP approximately zero (mean ~0.0065 in 2000), consistent with Shaikh &amp; Tonak (2002). Period 2001-2012: historically unprecedented positive NSW/GDP, rising to 8.6% of GDP in 2010 (peak). Mean NSW/GDP for the full 1959-2012 period is 2.0%, driven almost entirely by the post-2001 deviation. Summary statistics for overlap 1959-1997: Moos series shows min=-1.2%, median=1.0%, mean=1.1%, max=3.7% (Shaikh &amp; Tonak original: min=-2.1%, median=-0.2%, mean=0.0%, max=2.9%). The ~1.1 pp mean difference is attributed to post-1999 NIPA revisions.</t>
+          <t>The mean NSW/GDP for the entire period is 2.0%, which represents a substantial shift from Shaikh and Tonak's finding of approximately zero. However, this overall mean masks an important structural break. As I will discuss further, the period 1959-2000 shows a mean NSW ≈ 0%, consistent with Shaikh and Tonak's findings. But the period 2001-2012 shows a mean NSW ≈ 5% of GDP, representing an unprecedented positive net transfer to workers.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 pp.4-5; full_transcription.md Section 3 Extended Net Social Wage Data Series</t>
+          <t>Moos 2017, Extended Data Series, p.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>validation_target</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V11 benchmark range for ST2 ES1301: expected 1959-1997 overlap mean of [0.008, 0.018], centered on Moos published value of 0.011. ST2 P21 achieves mean=0.013 (within 0.002 of target). The post-2001 rise to ~8.6% of GDP in 2010 should be reproduced with extended NIPA data. Structural shift across 2001 regime boundary is a key qualitative target.</t>
+          <t>Moos (2017) replicates and extends Shaikh &amp; Tonak (2002), computing NSW/GDP for 1959-2012. The methodology follows Shaikh &amp; Tonak: NSW = E1 + E2*LS - T1 - T2*LS, where E1 = direct labor benefits entirely allocated to labor (income support, Social Security, public assistance, housing); E2 = social consumption expenditures partially allocated by labor share LS; T1 = employee + employer Social Security contributions; T2 = personal income and property taxes allocated by LS. Moos primarily uses NSW/GDP as the denominator (citing Shaikh 2003), whereas Shaikh &amp; Tonak (2002) primarily used NSW/EC.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-013; series_registry.json ES1301 validation.reference_values</t>
+          <t>Moos_2017, Section 2 pp.3-4; full_transcription.md Section 2 Net Social Wage Methodology; [internal-decision-log] [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>causal_analysis</t>
+          <t>decision_reference</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Moos (2017) investigates four drivers of the post-2001 positive NSW/GDP: (1) Growth of income support — largest component, rising from 2.5% to 12.5% of GDP over study period; driven by Social Security, Medicare, Medicaid, SNAP, and refundable tax credits (EITC grew from $1.3bn in 1980 to $96.5bn in 2010). (2) Healthcare inflation — Medicare costs grew 14x from 1980 to 2010; Medicaid 17x; healthcare inflation 6.6%/year 2000-2010 exceeding GDP growth. (3) Neoliberal tax cuts — Bush EGTRRA (2001) and JGTRRA (2003) reduced income tax revenue sharply; extended under Obama. (4) Unemployment intensity — 2010 intensity=31.46% vs 1983 intensity=18.95% despite identical 9.6% unemployment rate, explaining why Great Recession produced 4x higher NSW/GDP than 1983 recession.</t>
+          <t>[internal-decision-record] (2026-05-06): The ST2 implementation (P21) uses NSW = E1 - (T1 + T2*LS) — direct social benefits minus taxes. Government consumption expenditure E2 (education, health, transportation from NIPA T3.16) is loaded by L17 but NOT included in the NSW computation. With E2 excluded, P21 produces a 1959-1997 overlap mean of 0.013, within 0.002 of Moos's published mean of 0.011. Including E2 at any positive alpha overshoots the 0.011 target substantially (at alpha=1.0 mean=0.071). The standard Shaikh-Tonak/Moos formula measures net fiscal transfer to workers: direct benefits minus taxes only.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 4 pp.6-23; full_transcription.md Sections 4.1-4.2</t>
+          <t>[internal-decision-log] [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Moos uses updated BEA NIPA tables (post-1999 comprehensive revision). Period 1959-2012. NSW expressed as ratio to GDP. Real NSW in 2010 constant dollars also computed. Labor share declines from high of 0.73 to low of 0.62 over period (secular neoliberal decline). Moos also computes NSW/GDP using Mohun (2016) alternative income share estimate as robustness check — results nearly identical, confirming findings are not artifacts of labor share choice.</t>
+          <t>Moos (2017) finds a major post-2001 structural break. Period 1959-2000: NSW/GDP approximately zero (mean ~0.0065 in 2000), consistent with Shaikh &amp; Tonak (2002). Period 2001-2012: historically unprecedented positive NSW/GDP, rising to 8.6% of GDP in 2010 (peak). Mean NSW/GDP for the full 1959-2012 period is 2.0%, driven almost entirely by the post-2001 deviation. Summary statistics for overlap 1959-1997: Moos series shows min=-1.2%, median=1.0%, mean=1.1%, max=3.7% (Shaikh &amp; Tonak original: min=-2.1%, median=-0.2%, mean=0.0%, max=2.9%). The ~1.1 pp mean difference is attributed to post-1999 NIPA revisions.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Moos_2017, pp.3-5, Section 4.3 pp.20-23; full_transcription.md Sections 3 and 4.3</t>
+          <t>Moos_2017, Section 3 pp.4-5; full_transcription.md Section 3 Extended Net Social Wage Data Series</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>theoretical_interpretation</t>
+          <t>validation_target</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moos interprets the positive 21st-century NSW through de Brunhoff (1978) and Kotz (2015) SSA theory: a positive NSW may indicate worsening worker conditions (state compensating for neoliberal wage suppression), not genuine redistribution. State must 'minimize or relocate the specifically proletarian risk.' Rising NSW/GDP in neoliberal era reflects: low wages requiring supplementation, dysfunctional healthcare system costs borne by state, and macroeconomic instability requiring countercyclical spending. A zero or modest NSW may indicate a better political-economic context for workers than a high positive NSW.</t>
+          <t>V11 benchmark range for ST2 ES1301: expected 1959-1997 overlap mean of [0.008, 0.018], centered on Moos published value of 0.011. ST2 P21 achieves mean=0.013 (within 0.002 of target). The post-2001 rise to ~8.6% of GDP in 2010 should be reproduced with extended NIPA data. Structural shift across 2001 regime boundary is a key qualitative target.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 5 pp.23-28; full_transcription.md Section 5 Discussion</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>[internal-decision-log] [internal-decision-record]; series_registry.json ES1301 validation.reference_values</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>causal_analysis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Moos (2017) investigates four drivers of the post-2001 positive NSW/GDP: (1) Growth of income support — largest component, rising from 2.5% to 12.5% of GDP over study period; driven by Social Security, Medicare, Medicaid, SNAP, and refundable tax credits (EITC grew from $1.3bn in 1980 to $96.5bn in 2010). (2) Healthcare inflation — Medicare costs grew 14x from 1980 to 2010; Medicaid 17x; healthcare inflation 6.6%/year 2000-2010 exceeding GDP growth. (3) Neoliberal tax cuts — Bush EGTRRA (2001) and JGTRRA (2003) reduced income tax revenue sharply; extended under Obama. (4) Unemployment intensity — 2010 intensity=31.46% vs 1983 intensity=18.95% despite identical 9.6% unemployment rate, explaining why Great Recession produced 4x higher NSW/GDP than 1983 recession.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 4 pp.6-23; full_transcription.md Sections 4.1-4.2</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NSW/GDP extended to 2012 by Moos (2017), replicating Shaikh &amp; Tonak methodology with post-1999 NIPA revision. 1959-2012 coverage. E2 excluded from NSW per DEC-013; standard formula NSW = E1 - T1 - T2*LS. 1959-1997 overlap mean = 0.013 in ST2 (Moos published = 0.011). Post-2001 structural break: unprecedented NSW rise to 8.6% of GDP in 2010.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
+          <t>Moos uses updated BEA NIPA tables (post-1999 comprehensive revision). Period 1959-2012. NSW expressed as ratio to GDP. Real NSW in 2010 constant dollars also computed. Labor share declines from high of 0.73 to low of 0.62 over period (secular neoliberal decline). Moos also computes NSW/GDP using Mohun (2016) alternative income share estimate as robustness check — results nearly identical, confirming findings are not artifacts of labor share choice.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Moos_2017, pp.3-5, Section 4.3 pp.20-23; full_transcription.md Sections 3 and 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>theoretical_interpretation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Moos interprets the positive 21st-century NSW through de Brunhoff (1978) and Kotz (2015) SSA theory: a positive NSW may indicate worsening worker conditions (state compensating for neoliberal wage suppression), not genuine redistribution. State must 'minimize or relocate the specifically proletarian risk.' Rising NSW/GDP in neoliberal era reflects: low wages requiring supplementation, dysfunctional healthcare system costs borne by state, and macroeconomic instability requiring countercyclical spending. A zero or modest NSW may indicate a better political-economic context for workers than a high positive NSW.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 5 pp.23-28; full_transcription.md Section 5 Discussion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NIPA vintage difference: Moos used ~2015 data pull; ST2 uses 2026 pull; minor differences in revised historical values expected</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>E2 loaded in L17 but excluded from NSW computation per DEC-013 — E2 data retained for future sensitivity analysis</t>
-        </is>
-      </c>
+          <t>This paper replicates the methodology and extends the data series in Shaikh and Tonak (2000) in order to examine fiscal transfers between the state and workers in the United States in the 21st century. Strikingly, the updated net social wage data reveals a sizable deviation starting in 2002, with much higher positive net social wages for a decade. In fact, the net social wage rises to a historic high of positive 8.6 percent of GDP in 2010.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Labor share secular decline from 0.73 to 0.62 over period; does not affect post-2001 findings (robustness confirmed with Mohun income share)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
+          <t>NetSocialWage = TotalLaborBenefits − TotalLaborTaxes    (1) ... TotalLaborBenefits = E1 + E2 ∗ LS    (2) ... TotalLaborTaxes = T1 + T2 ∗ LS    (3)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The mean NSW/GDP for the entire period is 2.0%, which represents a substantial shift from Shaikh and Tonak's finding of approximately zero. However, this overall mean masks an important structural break. As I will discuss further, the period 1959-2000 shows a mean NSW ≈ 0%, consistent with Shaikh and Tonak's findings. But the period 2001-2012 shows a mean NSW ≈ 5% of GDP, representing an unprecedented positive net transfer to workers.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1302</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ES1304</t>
-        </is>
-      </c>
-    </row>
+          <t>NSW/GDP extended to 2012 by Moos (2017), replicating Shaikh &amp; Tonak methodology with post-1999 NIPA revision. 1959-2012 coverage. E2 excluded from NSW per [internal-decision-record]; standard formula NSW = E1 - T1 - T2*LS. 1959-1997 overlap mean = 0.013 in ST2 (Moos published = 0.011). Post-2001 structural break: unprecedented NSW rise to 8.6% of GDP in 2010.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ES1305</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1450,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ES1201</t>
+          <t>NIPA vintage difference: Moos used ~2015 data pull; ST2 uses 2026 pull; minor differences in revised historical values expected</t>
         </is>
       </c>
     </row>
@@ -1405,49 +1458,105 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S607</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+          <t>E2 loaded in L17 but excluded from NSW computation per [internal-decision-record] — E2 data retained for future sensitivity analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Labor share secular decline from 0.73 to 0.62 over period; does not affect post-2001 findings (robustness confirmed with Mohun income share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES1302</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES1304</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES1305</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ES1201</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Moos, Katherine A. 2017. 'Neoliberal Redistributive Policy: The U.S. Net Social Wage in the 21st Century.' Working Paper No. 2017-18, Department of Economics, University of Massachusetts Amherst. September 18, 2017.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>ST_2002</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism. M.E. Sharpe, Armonk. pp. 247-265.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. Survey of Current Business, various years.</t>
         </is>
@@ -1464,11 +1573,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1535,7 +1644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1665,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1959_1997_mean": 0.011}</t>
+          <t>{"1959": -0.0145509124183207, "2012": 0.0672641204739599}</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1689,55 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>derived_statistics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"1959_1997_mean": 0.011}</t>
         </is>
       </c>
     </row>
